--- a/scripts/rename-students/inputs/student-name-updates.xlsx
+++ b/scripts/rename-students/inputs/student-name-updates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\rename-students\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082BB95F-7E72-400D-A422-98C453772D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F944A30-2601-4DBD-9492-4CD5819BB30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4920" yWindow="90" windowWidth="9315" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="updates" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>nationalId</t>
   </si>
@@ -33,107 +33,17 @@
     <t>newDisplayName</t>
   </si>
   <si>
-    <t>1207010461</t>
+    <t>لين أحمد عبداللطيف النافع</t>
   </si>
   <si>
-    <t>لمى وليد منصور البصري</t>
-  </si>
-  <si>
-    <t>1208683589</t>
-  </si>
-  <si>
-    <t>لانا سلطان فهد المطيري</t>
-  </si>
-  <si>
-    <t>1203999477</t>
-  </si>
-  <si>
-    <t>ورد ناصر حاتم الحبردي</t>
-  </si>
-  <si>
-    <t>1201022520</t>
-  </si>
-  <si>
-    <t>ألماس سلمان ناصر الحلافي</t>
-  </si>
-  <si>
-    <t>1201706106</t>
-  </si>
-  <si>
-    <t>تالا عبدالله رومي الرومي</t>
-  </si>
-  <si>
-    <t>1199441161</t>
-  </si>
-  <si>
-    <t>إيلاف ضويحي صالح الفحام</t>
-  </si>
-  <si>
-    <t>1200572459</t>
-  </si>
-  <si>
-    <t>بسمة ماجد عبدالرحمن الخمشي</t>
-  </si>
-  <si>
-    <t>1201793906</t>
-  </si>
-  <si>
-    <t>عبدالعزيز عبدالله سالم العتيبي</t>
-  </si>
-  <si>
-    <t>1201843560</t>
-  </si>
-  <si>
-    <t>مازن عبدالمجيد عبدالمحسن الحلافي</t>
-  </si>
-  <si>
-    <t>1201130760</t>
-  </si>
-  <si>
-    <t>ميس مصعب مدالله المديد</t>
-  </si>
-  <si>
-    <t>1203527690</t>
-  </si>
-  <si>
-    <t>توق ماجد فهد المحلسي</t>
-  </si>
-  <si>
-    <t>1203406382</t>
-  </si>
-  <si>
-    <t>صالح عادل عبدالله الخمشي</t>
-  </si>
-  <si>
-    <t>1200298543</t>
-  </si>
-  <si>
-    <t>فارس احمد مدالله الخميس</t>
-  </si>
-  <si>
-    <t>1202411458</t>
-  </si>
-  <si>
-    <t>رولا عبداللطيف سليمان الفهد</t>
-  </si>
-  <si>
-    <t>1202605505</t>
-  </si>
-  <si>
-    <t>شريفة راشد حمود الجارالله</t>
-  </si>
-  <si>
-    <t>1203960627</t>
-  </si>
-  <si>
-    <t>علي علي علي العتيبي</t>
+    <t>1207533553</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,15 +51,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF222222"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -162,14 +65,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor theme="6" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -177,22 +74,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="6" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="6" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -200,15 +86,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -489,10 +367,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -506,130 +384,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
